--- a/financial.xlsx
+++ b/financial.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042925F8-0498-4975-B761-16066D550A76}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445DDADF-B758-463B-93C6-CC3BF91FBCFC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Question" sheetId="1" r:id="rId1"/>
@@ -303,6 +303,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -318,9 +321,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,15 +453,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>38101</xdr:rowOff>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>161926</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -489,7 +489,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="104775" y="5019675"/>
+          <a:off x="257175" y="0"/>
           <a:ext cx="6886575" cy="3400426"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -977,7 +977,7 @@
       <c r="M16" t="s">
         <v>20</v>
       </c>
-      <c r="N16" s="23">
+      <c r="N16" s="18">
         <v>0.13500000000000001</v>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
     </row>
     <row r="21" spans="12:18" x14ac:dyDescent="0.25">
-      <c r="M21" s="24">
+      <c r="M21" s="19">
         <v>1</v>
       </c>
       <c r="N21" s="17">
@@ -1032,7 +1032,7 @@
       </c>
     </row>
     <row r="22" spans="12:18" x14ac:dyDescent="0.25">
-      <c r="M22" s="24">
+      <c r="M22" s="19">
         <v>2</v>
       </c>
       <c r="N22" s="17">
@@ -1045,7 +1045,7 @@
       </c>
     </row>
     <row r="23" spans="12:18" x14ac:dyDescent="0.25">
-      <c r="M23" s="24">
+      <c r="M23" s="19">
         <v>3</v>
       </c>
       <c r="N23" s="17">
@@ -1058,7 +1058,7 @@
       </c>
     </row>
     <row r="24" spans="12:18" x14ac:dyDescent="0.25">
-      <c r="M24" s="24">
+      <c r="M24" s="19">
         <v>4</v>
       </c>
       <c r="N24" s="17">
@@ -1071,7 +1071,7 @@
       </c>
     </row>
     <row r="25" spans="12:18" x14ac:dyDescent="0.25">
-      <c r="M25" s="24">
+      <c r="M25" s="19">
         <v>5</v>
       </c>
       <c r="N25" s="17">
@@ -1084,7 +1084,7 @@
       </c>
     </row>
     <row r="26" spans="12:18" x14ac:dyDescent="0.25">
-      <c r="M26" s="24">
+      <c r="M26" s="19">
         <v>6</v>
       </c>
       <c r="N26" s="17">
@@ -1097,7 +1097,7 @@
       </c>
     </row>
     <row r="27" spans="12:18" x14ac:dyDescent="0.25">
-      <c r="M27" s="24">
+      <c r="M27" s="19">
         <v>7</v>
       </c>
       <c r="N27" s="17">
@@ -1110,7 +1110,7 @@
       </c>
     </row>
     <row r="28" spans="12:18" x14ac:dyDescent="0.25">
-      <c r="M28" s="24">
+      <c r="M28" s="19">
         <v>8</v>
       </c>
       <c r="N28" s="17">
@@ -1123,7 +1123,7 @@
       </c>
     </row>
     <row r="29" spans="12:18" x14ac:dyDescent="0.25">
-      <c r="M29" s="24">
+      <c r="M29" s="19">
         <v>9</v>
       </c>
       <c r="N29" s="17">
@@ -1136,7 +1136,7 @@
       </c>
     </row>
     <row r="30" spans="12:18" x14ac:dyDescent="0.25">
-      <c r="M30" s="24">
+      <c r="M30" s="19">
         <v>10</v>
       </c>
       <c r="N30" s="17">
@@ -1149,7 +1149,7 @@
       </c>
     </row>
     <row r="31" spans="12:18" x14ac:dyDescent="0.25">
-      <c r="M31" s="24">
+      <c r="M31" s="19">
         <v>11</v>
       </c>
       <c r="N31" s="17">
@@ -1162,7 +1162,7 @@
       </c>
     </row>
     <row r="32" spans="12:18" x14ac:dyDescent="0.25">
-      <c r="M32" s="24">
+      <c r="M32" s="19">
         <v>12</v>
       </c>
       <c r="N32" s="17">
@@ -1175,7 +1175,7 @@
       </c>
     </row>
     <row r="33" spans="12:15" x14ac:dyDescent="0.25">
-      <c r="M33" s="24">
+      <c r="M33" s="19">
         <v>13</v>
       </c>
       <c r="N33" s="17">
@@ -1188,7 +1188,7 @@
       </c>
     </row>
     <row r="34" spans="12:15" x14ac:dyDescent="0.25">
-      <c r="M34" s="24">
+      <c r="M34" s="19">
         <v>14</v>
       </c>
       <c r="N34" s="17">
@@ -1201,7 +1201,7 @@
       </c>
     </row>
     <row r="35" spans="12:15" x14ac:dyDescent="0.25">
-      <c r="M35" s="24">
+      <c r="M35" s="19">
         <v>15</v>
       </c>
       <c r="N35" s="17">
@@ -1214,7 +1214,7 @@
       </c>
     </row>
     <row r="36" spans="12:15" x14ac:dyDescent="0.25">
-      <c r="M36" s="24">
+      <c r="M36" s="19">
         <v>16</v>
       </c>
       <c r="N36" s="17">
@@ -1227,7 +1227,7 @@
       </c>
     </row>
     <row r="37" spans="12:15" x14ac:dyDescent="0.25">
-      <c r="M37" s="24">
+      <c r="M37" s="19">
         <v>17</v>
       </c>
       <c r="N37" s="17">
@@ -1240,7 +1240,7 @@
       </c>
     </row>
     <row r="38" spans="12:15" x14ac:dyDescent="0.25">
-      <c r="M38" s="24">
+      <c r="M38" s="19">
         <v>18</v>
       </c>
       <c r="N38" s="17">
@@ -1253,7 +1253,7 @@
       </c>
     </row>
     <row r="39" spans="12:15" x14ac:dyDescent="0.25">
-      <c r="M39" s="24">
+      <c r="M39" s="19">
         <v>19</v>
       </c>
       <c r="N39" s="17">
@@ -1266,7 +1266,7 @@
       </c>
     </row>
     <row r="40" spans="12:15" x14ac:dyDescent="0.25">
-      <c r="M40" s="24">
+      <c r="M40" s="19">
         <v>20</v>
       </c>
       <c r="N40" s="17">
@@ -1279,7 +1279,7 @@
       </c>
     </row>
     <row r="41" spans="12:15" x14ac:dyDescent="0.25">
-      <c r="M41" s="24">
+      <c r="M41" s="19">
         <v>21</v>
       </c>
       <c r="N41" s="17">
@@ -1292,7 +1292,7 @@
       </c>
     </row>
     <row r="42" spans="12:15" x14ac:dyDescent="0.25">
-      <c r="M42" s="24">
+      <c r="M42" s="19">
         <v>22</v>
       </c>
       <c r="N42" s="17">
@@ -1305,7 +1305,7 @@
       </c>
     </row>
     <row r="43" spans="12:15" x14ac:dyDescent="0.25">
-      <c r="M43" s="24">
+      <c r="M43" s="19">
         <v>23</v>
       </c>
       <c r="N43" s="17">
@@ -1318,7 +1318,7 @@
       </c>
     </row>
     <row r="44" spans="12:15" x14ac:dyDescent="0.25">
-      <c r="M44" s="24">
+      <c r="M44" s="19">
         <v>24</v>
       </c>
       <c r="N44" s="17">
@@ -1334,7 +1334,7 @@
       <c r="L46" t="s">
         <v>32</v>
       </c>
-      <c r="M46" s="25"/>
+      <c r="M46" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1387,20 +1387,20 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="8"/>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="8"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -1434,12 +1434,12 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="8"/>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -1461,22 +1461,22 @@
       <c r="F15" s="9"/>
     </row>
     <row r="16" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="22"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="25"/>
     </row>
     <row r="17" spans="1:6" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="20"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="22"/>
+      <c r="A17" s="23"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="25"/>
     </row>
     <row r="18" spans="1:6" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10"/>
